--- a/core_board/core_board_BOM(REAL).xlsx
+++ b/core_board/core_board_BOM(REAL).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blaydn\Documents\Github\CoreBoard_Hardware\core_board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A8DE626-9D3E-48CB-9BD9-62D23550D32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C53CF311-7E4D-4BC2-B2ED-FD23C5F4EDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A4DC107-8EC3-4C2E-B61B-81E673112C2C}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="123">
   <si>
     <t>Reference</t>
   </si>
@@ -31,21 +31,6 @@
     <t>Value</t>
   </si>
   <si>
-    <t>DNP</t>
-  </si>
-  <si>
-    <t>Exclude from BOM</t>
-  </si>
-  <si>
-    <t>Exclude from Board</t>
-  </si>
-  <si>
-    <t>Exclude from Simulation</t>
-  </si>
-  <si>
-    <t>Exclude from Position Files</t>
-  </si>
-  <si>
     <t>Footprint</t>
   </si>
   <si>
@@ -58,9 +43,6 @@
     <t>10uF</t>
   </si>
   <si>
-    <t>${EXCLUDE_FROM_POS_FILES}</t>
-  </si>
-  <si>
     <t>Capacitor_SMD:C_0603_1608Metric_Pad1.08x0.95mm_HandSolder</t>
   </si>
   <si>
@@ -389,13 +371,34 @@
   </si>
   <si>
     <t>MRDT_Drill_Holes:4_40_Hole_Pad_Via</t>
+  </si>
+  <si>
+    <t>Price per Component</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t>Total:</t>
+  </si>
+  <si>
+    <t>https://www.codaca.com/Private/pdf/CSBA1050.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total: </t>
+  </si>
+  <si>
+    <t>Standard Components:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,6 +533,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -828,7 +839,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -871,11 +882,25 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -909,6 +934,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1249,811 +1275,1024 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4D820C-9AE0-48CD-BB82-BF0CC29D7809}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="58.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <f>IF(F2= "~", "~", (E2*F2))</f>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <f t="shared" ref="G3:G45" si="0">IF(F3= "~", "~", (E3*F3))</f>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="F18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="0"/>
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33">
         <v>10</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="3">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="3">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>5.61</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="0"/>
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G41" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="G42" s="2">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>25</v>
+      </c>
+      <c r="G43" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.55</v>
+      </c>
+      <c r="G44" s="2">
+        <f t="shared" si="0"/>
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="2">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" t="s">
-        <v>71</v>
-      </c>
-      <c r="J24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I26" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-      <c r="H27" t="s">
-        <v>12</v>
-      </c>
-      <c r="I27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-      <c r="H32" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33" t="s">
-        <v>12</v>
-      </c>
-      <c r="I33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34">
-        <v>10</v>
-      </c>
-      <c r="C34">
-        <v>100</v>
-      </c>
-      <c r="H34" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35">
-        <v>4</v>
-      </c>
-      <c r="C35">
-        <v>220</v>
-      </c>
-      <c r="H35" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>94</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="H36" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-      <c r="H37" t="s">
-        <v>12</v>
-      </c>
-      <c r="I37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" t="s">
-        <v>12</v>
-      </c>
-      <c r="I38" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="H39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I39" t="s">
-        <v>102</v>
-      </c>
-      <c r="J39" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
-      </c>
-      <c r="H40" t="s">
-        <v>12</v>
-      </c>
-      <c r="I40" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>107</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>108</v>
-      </c>
-      <c r="H41" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" t="s">
-        <v>109</v>
-      </c>
-      <c r="J41" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>111</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" t="s">
-        <v>12</v>
-      </c>
-      <c r="I42" t="s">
-        <v>113</v>
-      </c>
-      <c r="J42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>12</v>
-      </c>
-      <c r="I43" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" t="s">
-        <v>12</v>
-      </c>
-      <c r="I44" t="s">
-        <v>119</v>
-      </c>
-      <c r="J44" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F47" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B45">
-        <v>4</v>
-      </c>
-      <c r="H45" t="s">
-        <v>12</v>
-      </c>
-      <c r="I45" t="s">
-        <v>122</v>
+      <c r="G47" s="2">
+        <f>SUM(G2:G46)</f>
+        <v>51.489999999999995</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D21" r:id="rId1" xr:uid="{8C3DF471-5930-4BA5-A426-1E7EAEC2CEC2}"/>
+    <hyperlink ref="D41" r:id="rId2" xr:uid="{1DBBCB26-ADA9-4877-9C5C-3F2BDDEF45E3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>